--- a/docs/ValueSet-BREstadoEvento-1.0.xlsx
+++ b/docs/ValueSet-BREstadoEvento-1.0.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -105,25 +105,49 @@
     <t>preparation</t>
   </si>
   <si>
+    <t>Preparation</t>
+  </si>
+  <si>
     <t>in-progress</t>
   </si>
   <si>
+    <t>In Progress</t>
+  </si>
+  <si>
     <t>not-done</t>
   </si>
   <si>
+    <t>Not Done</t>
+  </si>
+  <si>
     <t>on-hold</t>
   </si>
   <si>
+    <t>On Hold</t>
+  </si>
+  <si>
     <t>stopped</t>
   </si>
   <si>
+    <t>Stopped</t>
+  </si>
+  <si>
     <t>completed</t>
   </si>
   <si>
+    <t>Completed</t>
+  </si>
+  <si>
     <t>unknown</t>
   </si>
   <si>
+    <t>Unknown</t>
+  </si>
+  <si>
     <t>entered-in-error</t>
+  </si>
+  <si>
+    <t>Entered in Error</t>
   </si>
   <si>
     <t/>
@@ -415,64 +439,80 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
